--- a/quant/vignettes/articles/report_norm.xlsx
+++ b/quant/vignettes/articles/report_norm.xlsx
@@ -643,7 +643,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2025-10-04 18:36:01.881535</t>
+          <t>2025-10-30 22:47:16.098381</t>
         </is>
       </c>
     </row>
